--- a/Project_ETF/ETF_Investment_Portfolio/00919/ETF_Investment_Portfolio_20260918.xlsx
+++ b/Project_ETF/ETF_Investment_Portfolio/00919/ETF_Investment_Portfolio_20260918.xlsx
@@ -1239,17 +1239,17 @@
     <row r="50">
       <c r="A50" s="3" t="inlineStr">
         <is>
-          <t>9941</t>
+          <t>2597</t>
         </is>
       </c>
       <c r="B50" s="3" t="inlineStr">
         <is>
-          <t>裕融</t>
+          <t>潤弘</t>
         </is>
       </c>
       <c r="C50" s="4" t="inlineStr">
         <is>
-          <t>30,838,800</t>
+          <t>14,300,000</t>
         </is>
       </c>
       <c r="D50" s="4" t="inlineStr">
@@ -1261,17 +1261,17 @@
     <row r="51">
       <c r="A51" s="3" t="inlineStr">
         <is>
-          <t>2597</t>
+          <t>9941</t>
         </is>
       </c>
       <c r="B51" s="3" t="inlineStr">
         <is>
-          <t>潤弘</t>
+          <t>裕融</t>
         </is>
       </c>
       <c r="C51" s="4" t="inlineStr">
         <is>
-          <t>14,300,000</t>
+          <t>30,838,800</t>
         </is>
       </c>
       <c r="D51" s="4" t="inlineStr">
@@ -1371,17 +1371,17 @@
     <row r="56">
       <c r="A56" s="3" t="inlineStr">
         <is>
-          <t>2458</t>
+          <t>4763</t>
         </is>
       </c>
       <c r="B56" s="3" t="inlineStr">
         <is>
-          <t>義隆</t>
+          <t>材料*-KY</t>
         </is>
       </c>
       <c r="C56" s="4" t="inlineStr">
         <is>
-          <t>15,520,000</t>
+          <t>41,500,000</t>
         </is>
       </c>
       <c r="D56" s="4" t="inlineStr">
@@ -1393,17 +1393,17 @@
     <row r="57">
       <c r="A57" s="3" t="inlineStr">
         <is>
-          <t>4763</t>
+          <t>2458</t>
         </is>
       </c>
       <c r="B57" s="3" t="inlineStr">
         <is>
-          <t>材料*-KY</t>
+          <t>義隆</t>
         </is>
       </c>
       <c r="C57" s="4" t="inlineStr">
         <is>
-          <t>41,500,000</t>
+          <t>15,520,000</t>
         </is>
       </c>
       <c r="D57" s="4" t="inlineStr">
